--- a/assets/templates/mof_r10.xlsx
+++ b/assets/templates/mof_r10.xlsx
@@ -561,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -718,6 +718,24 @@
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -6581,7 +6599,7 @@
       <c r="B9" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="42"/>
+      <c r="D9" s="87"/>
       <c r="E9" s="42"/>
       <c r="O9" s="16"/>
     </row>
@@ -6596,13 +6614,14 @@
       <c r="G10" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="57"/>
+      <c r="H10" s="88"/>
       <c r="I10" s="57"/>
       <c r="J10" s="57"/>
       <c r="L10" s="57" t="s">
         <v>18</v>
       </c>
       <c r="M10" s="57"/>
+      <c r="N10" s="89"/>
       <c r="O10" s="16"/>
     </row>
     <row r="11" spans="2:15" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6633,20 +6652,21 @@
         <v>20</v>
       </c>
       <c r="C13" s="57"/>
-      <c r="D13"/>
+      <c r="D13" s="89"/>
       <c r="E13" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F13"/>
+      <c r="F13" s="89"/>
       <c r="H13" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J13" s="42"/>
+      <c r="J13" s="87"/>
       <c r="K13" s="42"/>
       <c r="L13" s="42"/>
       <c r="M13" s="17" t="s">
         <v>29</v>
       </c>
+      <c r="N13" s="89"/>
       <c r="O13" s="16"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.3">
@@ -6654,14 +6674,15 @@
         <v>21</v>
       </c>
       <c r="C14" s="57"/>
-      <c r="D14"/>
+      <c r="D14" s="89"/>
       <c r="E14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F14"/>
+      <c r="F14" s="89"/>
       <c r="H14" s="17" t="s">
         <v>28</v>
       </c>
+      <c r="J14" s="89"/>
       <c r="K14" s="42" t="s">
         <v>68</v>
       </c>
@@ -6669,7 +6690,7 @@
       <c r="M14" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="N14"/>
+      <c r="N14" s="89"/>
       <c r="O14" s="16"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.3">
@@ -6677,17 +6698,19 @@
         <v>22</v>
       </c>
       <c r="C15" s="57"/>
+      <c r="D15" s="89"/>
       <c r="E15" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="F15"/>
+      <c r="F15" s="89"/>
       <c r="H15" s="17" t="s">
         <v>18</v>
       </c>
+      <c r="I15" s="89"/>
       <c r="M15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="N15" s="42"/>
+      <c r="N15" s="87"/>
       <c r="O15" s="43"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.3">
@@ -6695,18 +6718,18 @@
         <v>23</v>
       </c>
       <c r="C16" s="69"/>
-      <c r="D16" s="7"/>
+      <c r="D16" s="90"/>
       <c r="E16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="7"/>
+      <c r="F16" s="90"/>
       <c r="G16" s="7"/>
       <c r="H16" s="18" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
-      <c r="K16" s="39"/>
+      <c r="K16" s="91"/>
       <c r="L16" s="39"/>
       <c r="M16" s="39"/>
       <c r="N16" s="39"/>
@@ -6772,21 +6795,21 @@
       <c r="B20" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C20"/>
+      <c r="C20" s="89"/>
       <c r="E20" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F20"/>
+      <c r="F20" s="89"/>
       <c r="G20" s="16"/>
       <c r="H20" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="I20" s="42"/>
+      <c r="I20" s="87"/>
       <c r="J20" s="42"/>
       <c r="L20" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="M20" s="42"/>
+      <c r="M20" s="87"/>
       <c r="N20" s="42"/>
       <c r="O20" s="16"/>
     </row>
@@ -7342,7 +7365,7 @@
         <v>16</v>
       </c>
       <c r="H52" s="23"/>
-      <c r="I52" s="23"/>
+      <c r="I52" s="92"/>
       <c r="J52" s="23"/>
       <c r="K52" s="23"/>
       <c r="L52" s="23"/>
